--- a/spreadsheets/domains/cramps-ast_CRAMPS-AST_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-ast_CRAMPS-AST_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R5fa1ccc641ae4087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rad86cc7bde0e4a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R9e24dda0a08e45ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rf850de0b077c45d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R603a18cea68a4af8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R18677e94f76d4966"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rb47689d3f13043a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R535dbc1baa39417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Rec58ec61d3574c3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="Rbe82c21dc51948bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Rb97e6883f020409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R517c64e635764fd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R6873e534caa94c32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rd7a003f2b5844a92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="Rf334f85fcb354c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R7b64ad4797d04772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Ra6bb2adb2f0549f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R56befbc69a884e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Re94aa652c6404a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R952b6322740d40ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>sky coverage bias; cadence bias; follow-up selection bias; calibration drift</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
